--- a/GATEWAY/A1#111O3ENTERPRISESRL/o3enterprise/ris/8.10.0/report-checklist.xlsx
+++ b/GATEWAY/A1#111O3ENTERPRISESRL/o3enterprise/ris/8.10.0/report-checklist.xlsx
@@ -4278,7 +4278,7 @@
         <v>SI</v>
       </c>
       <c r="S50" s="34" t="str">
-        <v>Integrazione dei dati mancanti</v>
+        <v>Recupero e integrazione dei valori mancanti</v>
       </c>
       <c r="T50" s="41"/>
       <c r="U50" s="34"/>
@@ -4320,13 +4320,28 @@
       </c>
       <c r="K51" s="41"/>
       <c r="L51" s="34"/>
-      <c r="M51" s="41"/>
-      <c r="N51" s="41"/>
-      <c r="O51" s="34"/>
-      <c r="P51" s="41"/>
-      <c r="Q51" s="41"/>
-      <c r="R51" s="41"/>
-      <c r="S51" s="34"/>
+      <c r="M51" s="41" t="str">
+        <v>SI</v>
+      </c>
+      <c r="N51" s="41" t="str">
+        <v>SI</v>
+      </c>
+      <c r="O51" s="34" t="str">
+        <v xml:space="preserve">L'utente visualizza una notifia di validazione fallita prima della firma del refeto.
+Lo stato di validazione è visibile dall'interfaccia di refertazione.</v>
+      </c>
+      <c r="P51" s="41" t="str">
+        <v>SI</v>
+      </c>
+      <c r="Q51" s="41" t="str">
+        <v>NO</v>
+      </c>
+      <c r="R51" s="41" t="str">
+        <v>SI</v>
+      </c>
+      <c r="S51" s="34" t="str">
+        <v>Recupero e integrazione dei valori mancanti</v>
+      </c>
       <c r="T51" s="41"/>
       <c r="U51" s="34"/>
       <c r="V51" s="34"/>
